--- a/template/Bang_cong_no_MAU_CHUAN.xlsx
+++ b/template/Bang_cong_no_MAU_CHUAN.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TRUSTANA VIỆT NAM</t>
+          <t>TRUSTANA VIETNAM</t>
         </is>
       </c>
     </row>
@@ -512,86 +512,86 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Accounts receivable</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Customers' Name</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Credit Term</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>1 - 30</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>31 - 60</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>61 - 90</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>91 - 120</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>120+</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Salesman</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>Lý do chưa thu hồi được công nợ</t>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Reason for late payment</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
